--- a/assets/constructions/examples/ctd_ds3.xlsx
+++ b/assets/constructions/examples/ctd_ds3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,11 +609,36 @@
           <t>hand</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6127K-d9.3</t>
+          <t>6123TF-d11.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -623,28 +648,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6127K</t>
+          <t>6123TF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
+          <t>PMKN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>35.725</v>
+        <v>39.875</v>
       </c>
       <c r="I2" t="n">
-        <v>3.841</v>
+        <v>3.467</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -655,7 +676,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TIALN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -668,7 +689,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -678,23 +699,23 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3 S LongChip</t>
+          <t>3 S</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>150</v>
       </c>
       <c r="V2" t="n">
-        <v>1.246</v>
+        <v>1.541</v>
       </c>
       <c r="W2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="X2" t="n">
-        <v>82.754</v>
+        <v>93.459</v>
       </c>
       <c r="Y2" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -720,7 +741,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>HA-9.3</t>
+          <t>HA-11.5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -731,46 +752,63 @@
       <c r="AJ2" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A1166-8</t>
+          <t>6127K-d14.8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A1166</t>
+          <t>6127K</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PNSH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>14.8</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>35</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+        <v>44.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>K 10/20</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -778,7 +816,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>TP-NORM 4</t>
+          <t>ILIX NORM</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -786,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>14.8</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -794,25 +832,27 @@
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3 S LongChip</t>
+        </is>
+      </c>
       <c r="U3" t="n">
         <v>150</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.983</v>
       </c>
       <c r="W3" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="X3" t="n">
-        <v>77.93000000000001</v>
+        <v>109.017</v>
       </c>
       <c r="Y3" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
@@ -820,7 +860,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2017/Общий каталог WALTER 2017</t>
+          <t>2015 / Ilix General Catalog</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -836,7 +876,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-14.8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -847,47 +887,56 @@
       <c r="AJ3" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>KN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1025 5.000</t>
+          <t>A1166-9.8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>A1166</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>PNSH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>VHM</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -896,7 +945,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>DIN 6539</t>
+          <t>TP-NORM 4</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -904,7 +953,7 @@
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -912,27 +961,25 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>GS200G</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>150</v>
       </c>
       <c r="V4" t="n">
-        <v>0.67</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="X4" t="n">
-        <v>61.33</v>
+        <v>87.69</v>
       </c>
       <c r="Y4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
@@ -940,7 +987,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2019 GUHRING СВЕРЛА</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -956,7 +1003,7 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>HA-5</t>
+          <t>HA-9.8</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -967,23 +1014,34 @@
       <c r="AJ4" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>PNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6123K-d9.9</t>
+          <t>TDT751A14000 WN15HD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6123K</t>
+          <t>TDT751A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -991,26 +1049,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PMK</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IT9-IT10</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>37.675</v>
+        <v>43</v>
       </c>
       <c r="I5" t="n">
-        <v>3.805</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>3.071</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>WN15HD</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>K 10/20</t>
+          <t>TDT751A</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1018,43 +1084,37 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ILIX NORM</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>9.9</v>
+        <v>14</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3 S</t>
-        </is>
-      </c>
+      <c r="S5" t="n">
+        <v>45</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="V5" t="n">
-        <v>1.327</v>
+        <v>3.5</v>
       </c>
       <c r="W5" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X5" t="n">
-        <v>87.673</v>
+        <v>103.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1064,7 +1124,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2015 / Ilix General Catalog</t>
+          <t>2018/Достижения RU</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1074,13 +1134,13 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>h7</t>
+          <t>m7</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HA-9.9</t>
+          <t>HA-14</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1091,52 +1151,57 @@
       <c r="AJ5" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6123K-d7</t>
+          <t>A1167A-6.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6123K</t>
+          <t>A1167A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PMK</t>
-        </is>
-      </c>
+          <t>KN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>32.75</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.678</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>K 10/20</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -1144,7 +1209,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ILIX NORM</t>
+          <t>TP-NORM 4</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1152,7 +1217,7 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1160,27 +1225,25 @@
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>3 S</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>150</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.844</v>
       </c>
       <c r="W6" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="X6" t="n">
-        <v>73.062</v>
+        <v>69.15600000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -1188,7 +1251,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2015 / Ilix General Catalog</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1204,7 +1267,7 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HA-7</t>
+          <t>HA-6.3</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1215,6 +1278,17 @@
       <c r="AJ6" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>KN</t>
         </is>
       </c>
     </row>
